--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104463_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104463_W1.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0791</v>
+        <v>7.4668</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6768</v>
+        <v>7.1171</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4023</v>
+        <v>0.3497</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4493</v>
+        <v>2.4571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2901</v>
+        <v>0.2846</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1592</v>
+        <v>2.1724</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4603</v>
+        <v>2.4284</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3857</v>
+        <v>2.354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.011</v>
+        <v>0.0286</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0956</v>
+        <v>-2.0693</v>
       </c>
       <c r="O2" t="n">
-        <v>2.0846</v>
+        <v>2.098</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>2.121</v>
+        <v>0.5168</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2956</v>
+        <v>0.7892</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1745</v>
+        <v>-0.2724</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3746</v>
+        <v>3.3547</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9209</v>
+        <v>3.8995</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5707</v>
+        <v>0.9175</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0114</v>
+        <v>0.1704</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5821</v>
+        <v>0.7471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7264</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0613</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3878</v>
+        <v>0.3819</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3387</v>
+        <v>0.3463</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7705</v>
+        <v>0.7752</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.266</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3992</v>
+        <v>-0.2115</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0385</v>
+        <v>-0.1009</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1078</v>
+        <v>0.8852</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0693</v>
+        <v>-0.9861</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6157</v>
+        <v>1.6277</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1516</v>
+        <v>-0.1467</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7673</v>
+        <v>1.7744</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4919</v>
+        <v>1.4851</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6062</v>
+        <v>-1.5946</v>
       </c>
       <c r="O4" t="n">
-        <v>1.73</v>
+        <v>1.7372</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0599</v>
+        <v>-0.0929</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3871</v>
+        <v>0.174</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3273</v>
+        <v>-0.2669</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4725</v>
+        <v>-0.6606</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6992</v>
+        <v>-1.4258</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2268</v>
+        <v>0.7652</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4487</v>
+        <v>1.6101</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.798</v>
+        <v>2.8748</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3493</v>
+        <v>-1.2647</v>
       </c>
       <c r="J5" t="n">
-        <v>0.056</v>
+        <v>0.4317</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0559</v>
+        <v>2.6889</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>-2.2572</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5047</v>
+        <v>1.1784</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.742</v>
+        <v>0.1859</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2373</v>
+        <v>0.9925</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6814</v>
+        <v>-0.5179</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8498</v>
+        <v>-0.2837</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5312</v>
+        <v>-0.2342</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4783</v>
+        <v>-0.387</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7712</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>M. THOMAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.48</v>
+        <v>-1.6557</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9054</v>
+        <v>-1.5504</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4254</v>
+        <v>-0.1052</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6094</v>
+        <v>-1.3938</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8729</v>
+        <v>-3.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2635</v>
+        <v>1.6371</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4543</v>
+        <v>-0.5606</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7014</v>
+        <v>0.0582</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2471</v>
+        <v>-0.6188</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1551</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1715</v>
+        <v>-3.0891</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9837</v>
+        <v>2.2559</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3428</v>
+        <v>-0.3937</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7984</v>
+        <v>0.2457</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5444</v>
+        <v>-0.6394</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3856</v>
+        <v>2.4082</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7071</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2673</v>
+        <v>-1.7627</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7557</v>
+        <v>-1.9958</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4884</v>
+        <v>0.2331</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.816</v>
+        <v>-0.4362</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9871</v>
+        <v>-0.7957</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.829</v>
+        <v>0.3594</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4461</v>
+        <v>0.0353</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.0764</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7117</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3699</v>
+        <v>-0.4715</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2526</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1172</v>
+        <v>0.2477</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1337</v>
+        <v>0.3776</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5383</v>
+        <v>-0.1189</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4047</v>
+        <v>0.4966</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7712</v>
+        <v>-1.4764</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. THOMAS</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5117</v>
+        <v>-2.2571</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9526</v>
+        <v>-2.5083</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5591</v>
+        <v>0.2512</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4097</v>
+        <v>-1.8107</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0463</v>
+        <v>-0.9825</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6366</v>
+        <v>-0.8282</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-1.4531</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6052</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8769</v>
+        <v>-0.3576</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.1187</v>
+        <v>-0.2446</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2418</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2439</v>
+        <v>-0.1277</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2026</v>
+        <v>-0.2812</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0413</v>
+        <v>0.1535</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4102</v>
+        <v>-0.7739</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1853</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>J. KLJAJIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0724</v>
+        <v>-2.8234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2553</v>
+        <v>-3.1797</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3277</v>
+        <v>0.3563</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7859</v>
+        <v>-0.5414</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1457</v>
+        <v>-3.1017</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3599</v>
+        <v>2.5604</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3984</v>
+        <v>-0.413</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5399</v>
+        <v>-2.2967</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9383</v>
+        <v>1.8837</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3875</v>
+        <v>-0.1284</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6857</v>
+        <v>-0.805</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2982</v>
+        <v>0.6766</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1503</v>
+        <v>-0.461</v>
       </c>
       <c r="T9" t="n">
-        <v>0.493</v>
+        <v>-0.4904</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3427</v>
+        <v>0.0294</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.1173</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. KLJAJIC</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2337</v>
+        <v>-2.9639</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5363</v>
+        <v>0.2318</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3026</v>
+        <v>-3.1957</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5326</v>
+        <v>-0.7812</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0994</v>
+        <v>-1.1432</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5669</v>
+        <v>0.3621</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3819</v>
+        <v>-0.4226</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2796</v>
+        <v>0.5236</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8977</v>
+        <v>-0.9463</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1507</v>
+        <v>-0.3585</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8198</v>
+        <v>-1.6668</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6691</v>
+        <v>1.3083</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8865</v>
+        <v>0.2451</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8861</v>
+        <v>0.4967</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0003</v>
+        <v>-0.2516</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-3.1107</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8719</v>
+        <v>-5.9804</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6424</v>
+        <v>-3.0969</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2295</v>
+        <v>-2.8834</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9643</v>
+        <v>-1.9653</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5699</v>
+        <v>-1.5737</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7428</v>
+        <v>-0.7739</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7926</v>
+        <v>0.7682</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2215</v>
+        <v>-1.1915</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.3624</v>
+        <v>-2.3419</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4124</v>
+        <v>-0.5111</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5898</v>
+        <v>0.0019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8227</v>
+        <v>-0.513</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.2212</v>
+        <v>-9.820399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4631</v>
+        <v>-5.352400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.758</v>
+        <v>-4.4678</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5563999999999998</v>
+        <v>-0.5054000000000007</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.847200000000001</v>
+        <v>-6.822600000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>6.2909</v>
+        <v>6.3171</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3483</v>
+        <v>1.1392</v>
       </c>
       <c r="K12" t="n">
-        <v>4.894</v>
+        <v>4.747</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.5456</v>
+        <v>-3.6077</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9046</v>
+        <v>-1.6448</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.741</v>
+        <v>-11.5695</v>
       </c>
       <c r="O12" t="n">
-        <v>9.836600000000001</v>
+        <v>9.9247</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.6707</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R12" t="n">
-        <v>6.805099999999999</v>
+        <v>6.829100000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6161</v>
+        <v>-1.2308</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0885</v>
+        <v>0.3217999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5275</v>
+        <v>-1.5525</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3778</v>
+        <v>-2.3932</v>
       </c>
       <c r="W12" t="n">
-        <v>5.753099999999999</v>
+        <v>5.7065</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.1309</v>
+        <v>-8.099600000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7352</v>
+        <v>5.9545</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2395</v>
+        <v>7.0797</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5043</v>
+        <v>-1.1252</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5839</v>
+        <v>1.5768</v>
       </c>
       <c r="H13" t="n">
-        <v>2.101</v>
+        <v>2.0968</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5171</v>
+        <v>-0.52</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4223</v>
+        <v>2.3934</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7636</v>
+        <v>2.7439</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8384</v>
+        <v>-0.8166</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3269</v>
+        <v>-0.0988</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0998</v>
+        <v>-0.2164</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2271</v>
+        <v>0.1176</v>
       </c>
       <c r="V13" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W13" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5465</v>
+        <v>2.7288</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1649</v>
+        <v>1.5453</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3816</v>
+        <v>1.1834</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.978</v>
+        <v>-0.6152</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2579</v>
+        <v>0.0601</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2799</v>
+        <v>-0.6753</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3591</v>
+        <v>-0.2988</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3126</v>
+        <v>1.1097</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6717</v>
+        <v>-1.4084</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3371</v>
+        <v>-0.3164</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9453</v>
+        <v>-1.0496</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3918</v>
+        <v>0.7331</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>2.271</v>
+        <v>-0.4983</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6866</v>
+        <v>-0.3349</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5845</v>
+        <v>-0.1634</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>2.0212</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2609</v>
+        <v>2.4419</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7357</v>
+        <v>0.819</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5252</v>
+        <v>1.6228</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0503</v>
+        <v>4.0441</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9121</v>
+        <v>2.9014</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1382</v>
+        <v>1.1427</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1401</v>
+        <v>3.1119</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1028</v>
+        <v>3.0747</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9102</v>
+        <v>0.9322</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2126</v>
+        <v>0.3962</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0907</v>
+        <v>0.2111</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1219</v>
+        <v>0.1851</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3086</v>
+        <v>1.7579</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6747</v>
+        <v>0.4954</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3662</v>
+        <v>1.2625</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.043</v>
+        <v>1.277</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0591</v>
+        <v>1.9473</v>
       </c>
       <c r="I16" t="n">
-        <v>0.016</v>
+        <v>-0.6703</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7745</v>
+        <v>0.974</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3668</v>
+        <v>1.6892</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4078</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8176</v>
+        <v>0.303</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4258</v>
+        <v>0.2581</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3918</v>
+        <v>0.0449</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5123</v>
+        <v>0.2532</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8075</v>
+        <v>-0.0234</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2952</v>
+        <v>0.2766</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1426</v>
+        <v>1.6207</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2716</v>
+        <v>0.6515</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8711</v>
+        <v>0.9691</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2763</v>
+        <v>-0.9935</v>
       </c>
       <c r="H17" t="n">
-        <v>1.948</v>
+        <v>-1.2798</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6717</v>
+        <v>0.2863</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9853</v>
+        <v>0.3246</v>
       </c>
       <c r="K17" t="n">
-        <v>1.697</v>
+        <v>-0.3457</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7117</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>0.291</v>
+        <v>-1.318</v>
       </c>
       <c r="N17" t="n">
-        <v>0.251</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04</v>
+        <v>-0.384</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3605</v>
+        <v>1.3669</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2601</v>
+        <v>0.2179</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1004</v>
+        <v>1.149</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0858</v>
+        <v>1.2217</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8791</v>
+        <v>1.063</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2068</v>
+        <v>0.1588</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6076</v>
+        <v>-0.0477</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0562</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6637999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2628</v>
+        <v>0.7532</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1287</v>
+        <v>0.3512</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3915</v>
+        <v>0.4019</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3447</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0725</v>
+        <v>-0.4169</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7277</v>
+        <v>-0.384</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1458</v>
+        <v>0.4272</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0434</v>
+        <v>0.2203</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1024</v>
+        <v>0.2069</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0246</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2955</v>
+        <v>0.9136</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5942</v>
+        <v>-1.0877</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2986</v>
+        <v>2.0013</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1919</v>
+        <v>0.4885</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1919</v>
+        <v>0.5078</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.0193</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0346</v>
+        <v>0.0577</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>0.8101</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.7524</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1573</v>
+        <v>0.4308</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>-0.3023</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.7331</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8768</v>
+        <v>0.8803</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7864</v>
+        <v>0.448</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.4324</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. DEKKER</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2949</v>
+        <v>-0.1421</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5784</v>
+        <v>0.1227</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8734</v>
+        <v>-0.2648</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6985</v>
+        <v>0.1924</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.1924</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.329</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.1209</v>
+        <v>0.0345</v>
       </c>
       <c r="K20" t="n">
-        <v>1.309</v>
+        <v>0.0345</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.4299</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4224</v>
+        <v>0.1579</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6785</v>
+        <v>0.1579</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1009</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7289</v>
+        <v>0.4378</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5425</v>
+        <v>0.3159</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1865</v>
+        <v>0.122</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0965</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0965</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1443</v>
+        <v>-0.3357</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4322</v>
+        <v>-1.5942</v>
       </c>
       <c r="F21" t="n">
-        <v>1.288</v>
+        <v>1.2585</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4763</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4977</v>
+        <v>1.4875</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0213</v>
+        <v>-2.4447</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0648</v>
+        <v>-0.929</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8139</v>
+        <v>2.1923</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.749</v>
+        <v>-3.1213</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4115</v>
+        <v>-0.0282</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3162</v>
+        <v>-0.7048</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7277</v>
+        <v>0.6766</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1669</v>
+        <v>0.5029</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0907</v>
+        <v>0.3363</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2577</v>
+        <v>0.1666</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2519</v>
+        <v>-0.7773</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1538</v>
+        <v>-0.9547</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9019</v>
+        <v>0.1773</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9557</v>
+        <v>-0.7469</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4833</v>
+        <v>-1.6599</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.439</v>
+        <v>0.913</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8987000000000001</v>
+        <v>-0.6198</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2094</v>
+        <v>-1.3864</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1081</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.057</v>
+        <v>-0.1271</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7261</v>
+        <v>-0.2734</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6691</v>
+        <v>0.1463</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4038</v>
+        <v>0.6933</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2571</v>
+        <v>-0.1072</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1467</v>
+        <v>0.8005</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2534</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4822</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>S. DEKKER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0528</v>
+        <v>-1.0108</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6372</v>
+        <v>-3.672</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4156</v>
+        <v>2.6612</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7395</v>
+        <v>-3.713</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6565</v>
+        <v>0.6345</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9169</v>
+        <v>-4.3475</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5938</v>
+        <v>-4.157</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.372</v>
+        <v>1.296</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7782</v>
+        <v>-5.453</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1458</v>
+        <v>0.444</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2844</v>
+        <v>-0.6615</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1387</v>
+        <v>1.1055</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5816</v>
+        <v>1.4227</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8166</v>
+        <v>0.485</v>
       </c>
       <c r="U23" t="n">
-        <v>0.235</v>
+        <v>0.9377</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-0.0863</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-0.0863</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.221</v>
+        <v>14.3732</v>
       </c>
       <c r="E24" t="n">
-        <v>4.758099999999997</v>
+        <v>4.467999999999996</v>
       </c>
       <c r="F24" t="n">
-        <v>6.4633</v>
+        <v>9.9049</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5563999999999998</v>
+        <v>0.5052999999999992</v>
       </c>
       <c r="H24" t="n">
-        <v>6.8472</v>
+        <v>6.822399999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.2909</v>
+        <v>-6.3171</v>
       </c>
       <c r="J24" t="n">
-        <v>1.904500000000001</v>
+        <v>1.6447</v>
       </c>
       <c r="K24" t="n">
-        <v>11.7412</v>
+        <v>11.5695</v>
       </c>
       <c r="L24" t="n">
-        <v>-9.836499999999999</v>
+        <v>-9.924800000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3482</v>
+        <v>-1.1393</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.893899999999999</v>
+        <v>-4.7469</v>
       </c>
       <c r="O24" t="n">
-        <v>3.545500000000001</v>
+        <v>3.6075</v>
       </c>
       <c r="P24" t="n">
-        <v>5.6708</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.805</v>
+        <v>-6.828899999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6161</v>
+        <v>5.7834</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5274</v>
+        <v>1.5526</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0888</v>
+        <v>4.231</v>
       </c>
       <c r="V24" t="n">
-        <v>2.377899999999999</v>
+        <v>2.3934</v>
       </c>
       <c r="W24" t="n">
-        <v>8.130799999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.7529</v>
+        <v>-5.706399999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104463_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104463_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-8.099600000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.0863</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104463_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-5.706399999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
